--- a/AAII_Financials/Yearly/MDIA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MDIA_YR_FIN.xlsx
@@ -2708,7 +2708,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>16700</v>
+        <v>17500</v>
       </c>
       <c r="E58" s="3">
         <v>6400</v>
@@ -2753,7 +2753,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>17300</v>
+        <v>16500</v>
       </c>
       <c r="E59" s="3">
         <v>14500</v>
@@ -2843,7 +2843,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>99300</v>
+        <v>100800</v>
       </c>
       <c r="E61" s="3">
         <v>107800</v>
@@ -2888,7 +2888,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>54400</v>
+        <v>52900</v>
       </c>
       <c r="E62" s="3">
         <v>77900</v>
